--- a/src/service_ia/training/under_over/inconsistent/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/under_over/inconsistent/fit/report_fit_grid.xlsx
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" min="14" max="14"/>
@@ -1688,35 +1688,23 @@
           <t>[0.59287605 0.54433775 0.57634536 ... 0.46737195 0.49770927 0.46472347]</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.5687378220394025</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.8408802369868811</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.5514848737163475</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.6661079450217902</t>
-        </is>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5687378220394025</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8408802369868811</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5514848737163475</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6661079450217902</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1743,6 +1731,1610 @@
        1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 7.21620871e-03, ...,
        9.99722454e-01, 9.99722454e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.96395894, 0.8548573 , ..., 0.1528718 , 0.1364167 ,
        0.08944036]), 'roc_auc': 0.6274596738063862}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('scaler', StandardScaler()), ('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=XGBClassifier(base_score=None,
+                                                                booster=None,
+                                                                callbacks=None,
+                                                                colsample_bylevel=None,
+                                                                colsample_bynode=None,
+                                                                colsample_bytree=0.5,
+                                                                device=None,
+                                                                early_stopping_rounds=None,
+                                                                enable_categorical=False,
+                                                                eval_metric=None,
+                                                                feature_types=None,
+                                                                feature...s=None,
+                                                                gamma=None,
+                                                                grow_policy=None,
+                                                                importance_type=None,
+                                                                interaction_constraints=None,
+                                                                learning_rate=0.2,
+                                                                max_bin=None,
+                                                                max_cat_threshold=None,
+                                                                max_cat_to_onehot=None,
+                                                                max_delta_step=None,
+                                                                max_depth=3,
+                                                                max_leaves=None,
+                                                                min_child_weight=None,
+                                                                missing=nan,
+                                                                monotone_constraints=None,
+                                                                multi_strategy=None,
+                                                                n_estimators=200,
+                                                                n_jobs=None,
+                                                                num_parallel_tree=None, ...)))])</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_xgb_calibrated_sigmoid.pkl</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[0.6504329  0.69480519 0.71320346 0.67857143 0.6836403 ]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.34561729, 0.30078197, 0.27994895, 0.26154947, 0.2658906 ]), 'score_time': array([0.02228355, 0.02226257, 0.02111292, 0.02120423, 0.02219009]), 'test_accuracy': array([0.6504329 , 0.69480519, 0.71320346, 0.67857143, 0.6836403 ]), 'test_precision': array([0.78479197, 0.797023  , 0.81843575, 0.79444444, 0.80397727]), 'test_recall': array([0.75972222, 0.81692094, 0.81276006, 0.79334258, 0.78611111]), 'test_f1': array([0.77205363, 0.80684932, 0.81558803, 0.79389313, 0.79494382]), 'test_roc_auc': array([0.549503  , 0.59176841, 0.57969569, 0.55891175, 0.563711  ]), 'test_average_precision': array([0.81136723, 0.83721313, 0.81663618, 0.82134607, 0.81779969]), 'test_neg_log_loss': array([-0.66827825, -0.65485593, -0.6605119 , -0.6674595 , -0.66048626]), 'test_neg_brier_score': array([-0.23723486, -0.23048194, -0.23335604, -0.23661629, -0.23337854]), 'test_f1_macro': array([0.51131684, 0.5400226 , 0.58540959, 0.5320817 , 0.55150035]), 'test_f1_weighted': array([0.6569231 , 0.68960727, 0.71444902, 0.67885477, 0.68786034]), 'test_balanced_accuracy': array([0.51221405, 0.53900234, 0.58618298, 0.53213927, 0.55315408])}</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[0.55358011 0.50555937 0.59314202 ... 0.52259232 0.53431945 0.54519348]</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.6841307642346829</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7997762863534675</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7937829586455731</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7967683521381808</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[[ 300  716]
+ [ 743 2860]]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.28763183125599234, 'recall': 0.2952755905511811, 'f1-score': 0.2914035939776591, 'support': 1016.0}, '1': {'precision': 0.7997762863534675, 'recall': 0.7937829586455731, 'f1-score': 0.7967683521381808, 'support': 3603.0}, 'accuracy': 0.6841307642346829, 'macro avg': {'precision': 0.5437040588047299, 'recall': 0.5445292745983771, 'f1-score': 0.54408597305792, 'support': 4619.0}, 'weighted avg': {'precision': 0.6871244642320052, 'recall': 0.6841307642346829, 'f1-score': 0.6856077991416253, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.77994369, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99444907e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.11838666, 0.12358811, 0.13276178, ..., 0.61329569, 0.61355019,
+       0.61530781]), 'average_precision': 0.8200737575258656}</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.       , 0.       , 0.       , ..., 0.9980315, 1.       ,
+       1.       ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 5.27338329e-03, ...,
+       9.99444907e-01, 9.99444907e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.61530781, 0.60886631, ..., 0.13880924, 0.13276178,
+       0.11838666]), 'roc_auc': 0.5686386672523553}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('scaler', StandardScaler()), ('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=XGBClassifier(base_score=None,
+                                                                booster=None,
+                                                                callbacks=None,
+                                                                colsample_bylevel=None,
+                                                                colsample_bynode=None,
+                                                                colsample_bytree=0.5,
+                                                                device=None,
+                                                                early_stopping_rounds=None,
+                                                                enable_categorical=False,
+                                                                eval_metric=None,
+                                                                feature_types=None,
+                                                                feature...
+                                                                grow_policy=None,
+                                                                importance_type=None,
+                                                                interaction_constraints=None,
+                                                                learning_rate=0.2,
+                                                                max_bin=None,
+                                                                max_cat_threshold=None,
+                                                                max_cat_to_onehot=None,
+                                                                max_delta_step=None,
+                                                                max_depth=3,
+                                                                max_leaves=None,
+                                                                min_child_weight=None,
+                                                                missing=nan,
+                                                                monotone_constraints=None,
+                                                                multi_strategy=None,
+                                                                n_estimators=200,
+                                                                n_jobs=None,
+                                                                num_parallel_tree=None, ...),
+                                        method='isotonic'))])</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_xgb_calibrated_isotonic.pkl</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[0.57575758 0.62878788 0.58766234 0.59415584 0.62080173]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.2844243 , 0.26671338, 0.25137711, 0.25663519, 0.25757003]), 'score_time': array([0.01963353, 0.02017641, 0.01914454, 0.01914001, 0.01910615]), 'test_accuracy': array([0.57575758, 0.62878788, 0.58766234, 0.59415584, 0.62080173]), 'test_precision': array([0.79285714, 0.80288462, 0.81481481, 0.80034722, 0.80833333]), 'test_recall': array([0.61666667, 0.69486824, 0.61026352, 0.63938974, 0.67361111]), 'test_f1': array([0.69375   , 0.74498141, 0.69785884, 0.71087124, 0.73484848]), 'test_roc_auc': array([0.55647808, 0.58323142, 0.58284539, 0.56067107, 0.56933155]), 'test_average_precision': array([0.81599389, 0.83425965, 0.81678348, 0.82153745, 0.8208817 ]), 'test_neg_log_loss': array([-0.6621554 , -0.63800119, -0.65552666, -0.65553838, -0.65381015]), 'test_neg_brier_score': array([-0.23525253, -0.22444235, -0.23154136, -0.23277154, -0.23162556]), 'test_f1_macro': array([0.50180458, 0.53153643, 0.5243979 , 0.51514524, 0.53472462]), 'test_f1_weighted': array([0.60899488, 0.65119498, 0.62164116, 0.62487042, 0.64682   ]), 'test_balanced_accuracy': array([0.52401961, 0.54447845, 0.55882634, 0.53644364, 0.55355432])}</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[0.55413656 0.47417985 0.72870988 ... 0.47412972 0.48668119 0.5331715 ]</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6014288807101104</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8037931034482758</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6469608659450458</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7168998923573735</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[[ 447  569]
+ [1272 2331]]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2600349040139616, 'recall': 0.43996062992125984, 'f1-score': 0.3268738574040219, 'support': 1016.0}, '1': {'precision': 0.8037931034482758, 'recall': 0.6469608659450458, 'f1-score': 0.7168998923573735, 'support': 3603.0}, 'accuracy': 0.6014288807101104, 'macro avg': {'precision': 0.5319140037311187, 'recall': 0.5434607479331528, 'f1-score': 0.5218868748806977, 'support': 4619.0}, 'weighted avg': {'precision': 0.684187489543694, 'recall': 0.6014288807101104, 'f1-score': 0.6311093637770302, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.78020788, 0.78037687, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.        , 1.        , 1.        , ..., 0.00305301, 0.00277546,
+       0.        ]), 'thresholds': array([0.14442798, 0.15225807, 0.1530744 , ..., 0.98461539, 0.98518518,
+       1.        ]), 'average_precision': 0.8212969749965431}</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.       , 0.       , 0.       , ..., 0.9980315, 0.9980315,
+       1.       ]), 'tpr': array([0.        , 0.00277546, 0.00333056, ..., 0.99944491, 1.        ,
+       1.        ]), 'thresholds': array([       inf, 1.        , 0.98461539, ..., 0.18164585, 0.1530744 ,
+       0.14442798]), 'roc_auc': 0.5702850970647819}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 XGBClassifier(base_score=None, booster=None, callbacks=None,
+                               colsample_bylevel=None, colsample_bynode=None,
+                               colsample_bytree=0.5, device=None,
+                               early_stopping_rounds=None,
+                               enable_categorical=False, eval_metric=None,
+                               feature_types=None, feature_weights=None,
+                               gamma=None, grow_policy=None,
+                               importance_type=None,
+                               interaction_constraints=None, learning_rate=0.2,
+                               max_bin=None, max_cat_threshold=None,
+                               max_cat_to_onehot=None, max_delta_step=None,
+                               max_depth=3, max_leaves=None,
+                               min_child_weight=None, missing=nan,
+                               monotone_constraints=None, multi_strategy=None,
+                               n_estimators=200, n_jobs=None,
+                               num_parallel_tree=None, ...))])</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_xgb.pkl</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[0.56709957 0.58658009 0.58333333 0.57359307 0.58071506]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.04937243, 0.04938769, 0.05266404, 0.05037594, 0.05034399]), 'score_time': array([0.02013946, 0.01109147, 0.01206493, 0.01716495, 0.01312447]), 'test_accuracy': array([0.56709957, 0.58658009, 0.58333333, 0.57359307, 0.58071506]), 'test_precision': array([0.80418251, 0.8043088 , 0.80545455, 0.79781421, 0.80327869]), 'test_recall': array([0.5875    , 0.62135922, 0.61442441, 0.6074896 , 0.6125    ]), 'test_f1': array([0.67897271, 0.70109546, 0.69708891, 0.68976378, 0.69503546]), 'test_roc_auc': array([0.56320125, 0.56003908, 0.57595157, 0.5676298 , 0.57962507]), 'test_average_precision': array([0.82015519, 0.82307273, 0.82301758, 0.82911508, 0.83144812]), 'test_neg_log_loss': array([-0.69069499, -0.67019231, -0.68007588, -0.67627712, -0.67138869]), 'test_neg_brier_score': array([-0.24616379, -0.2392273 , -0.24112553, -0.24114348, -0.23918773]), 'test_f1_macro': array([0.50726044, 0.51546001, 0.51492227, 0.50405144, 0.51216244]), 'test_f1_weighted': array([0.60315171, 0.61952837, 0.61704599, 0.6081629 , 0.61459511]), 'test_balanced_accuracy': array([0.54129902, 0.54220671, 0.54366541, 0.53034578, 0.54024015])}</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[0.73382264 0.44375458 0.9378404  ... 0.7221319  0.5589767  0.5464375 ]</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5782636934401385</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8030025631636764</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6086594504579517</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6924534259551626</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[[ 478  538]
+ [1410 2193]]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2531779661016949, 'recall': 0.4704724409448819, 'f1-score': 0.32920110192837465, 'support': 1016.0}, '1': {'precision': 0.8030025631636764, 'recall': 0.6086594504579517, 'f1-score': 0.6924534259551626, 'support': 3603.0}, 'accuracy': 0.5782636934401385, 'macro avg': {'precision': 0.5280902646326856, 'recall': 0.5395659457014168, 'f1-score': 0.5108272639417686, 'support': 4619.0}, 'weighted avg': {'precision': 0.6820625781853319, 'recall': 0.5782636934401385, 'f1-score': 0.6125520704212339, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.78020788, 0.78016028, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 1.00000000e+00, 9.99722454e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.03774856, 0.0378698 , 0.04888155, ..., 0.9974584 , 0.9975441 ,
+       0.99907   ], dtype=float32), 'average_precision': 0.8242345585936561}</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99901575, 0.99901575,
+       1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 8.32639467e-04, ...,
+       9.98334721e-01, 1.00000000e+00, 1.00000000e+00]), 'thresholds': array([       inf, 0.99907   , 0.9974584 , ..., 0.08124176, 0.0378698 ,
+       0.03774856], dtype=float32), 'roc_auc': 0.5689298725253016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=GradientBoostingClassifier(learning_rate=0.05,
+                                                                             max_depth=5,
+                                                                             n_estimators=400,
+                                                                             subsample=0.7)))])</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_gb_calibrated_sigmoid.pkl</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[0.62445887 0.64393939 0.6547619  0.6547619  0.64463705]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([12.89575267, 12.82291222, 12.79996753, 12.79043531, 12.78914571]), 'score_time': array([0.06492877, 0.06477547, 0.06361365, 0.06527519, 0.06430888]), 'test_accuracy': array([0.63528139, 0.6547619 , 0.6525974 , 0.6525974 , 0.63271939]), 'test_precision': array([0.79782271, 0.79821958, 0.80395137, 0.7994012 , 0.80577849]), 'test_recall': array([0.7125    , 0.74618585, 0.73370319, 0.740638  , 0.69722222]), 'test_f1': array([0.75275128, 0.77132616, 0.76722263, 0.76889849, 0.74758004]), 'test_roc_auc': array([0.56706836, 0.5603397 , 0.57552114, 0.56074281, 0.58563903]), 'test_average_precision': array([0.8205027 , 0.82199836, 0.81916869, 0.82377546, 0.82745361]), 'test_neg_log_loss': array([-0.6348059 , -0.62276632, -0.62524613, -0.62949704, -0.63212612]), 'test_neg_brier_score': array([-0.22216978, -0.21717101, -0.21727655, -0.22031955, -0.22113262]), 'test_f1_macro': array([0.52895296, 0.53356595, 0.54139383, 0.53477604, 0.53681189]), 'test_f1_weighted': array([0.65393125, 0.66685577, 0.66799482, 0.6660265 , 0.65486946]), 'test_balanced_accuracy': array([0.53762255, 0.53811756, 0.5491176 , 0.54026974, 0.55058155])}</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[0.74718603 0.50761812 0.78699943 ... 0.64244555 0.63739959 0.716664  ]</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6505737172548171</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8023715415019763</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.7324451845684152</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7658154381892048</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[[ 366  650]
+ [ 964 2639]]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.27518796992481204, 'recall': 0.36023622047244097, 'f1-score': 0.31202046035805625, 'support': 1016.0}, '1': {'precision': 0.8023715415019763, 'recall': 0.7324451845684152, 'f1-score': 0.7658154381892048, 'support': 3603.0}, 'accuracy': 0.650573717254817, 'macro avg': {'precision': 0.5387797557133942, 'recall': 0.5463407025204281, 'f1-score': 0.5389179492736306, 'support': 4619.0}, 'weighted avg': {'precision': 0.6864116998214396, 'recall': 0.650573717254817, 'f1-score': 0.6659982272179021, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.78020788, 0.78016028, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 1.00000000e+00, 9.99722454e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.0789528 , 0.10668537, 0.11526206, ..., 0.98002437, 0.98023036,
+       0.98803116]), 'average_precision': 0.8225895954562527}</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99901575, 0.99901575,
+       1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 2.49791840e-03, ...,
+       9.99444907e-01, 1.00000000e+00, 1.00000000e+00]), 'thresholds': array([       inf, 0.98803116, 0.96105803, ..., 0.13774971, 0.10668537,
+       0.0789528 ]), 'roc_auc': 0.5724098574897122}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=GradientBoostingClassifier(learning_rate=0.05,
+                                                                             max_depth=5,
+                                                                             n_estimators=400,
+                                                                             subsample=0.7),
+                                        method='isotonic'))])</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_gb_calibrated_isotonic.pkl</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[0.62121212 0.64285714 0.63311688 0.64285714 0.62621885]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([12.94861364, 12.9915309 , 13.01883769, 13.00610256, 13.86550784]), 'score_time': array([0.06499195, 0.06496   , 0.06503272, 0.06836271, 0.06843615]), 'test_accuracy': array([0.60930736, 0.63744589, 0.63095238, 0.6461039 , 0.6099675 ]), 'test_precision': array([0.78904992, 0.79601227, 0.79968454, 0.80030488, 0.81468531]), 'test_recall': array([0.68055556, 0.71983356, 0.70319001, 0.72815534, 0.64722222]), 'test_f1': array([0.73079791, 0.75600874, 0.74833948, 0.76252723, 0.72136223]), 'test_roc_auc': array([0.55894608, 0.560572  , 0.5693003 , 0.56597979, 0.59045567]), 'test_average_precision': array([0.81890255, 0.82439524, 0.81608471, 0.82763705, 0.82856613]), 'test_neg_log_loss': array([-0.67907662, -0.62597294, -0.64023897, -0.62877359, -0.63959747]), 'test_neg_brier_score': array([-0.22595229, -0.21936582, -0.2220342 , -0.22009132, -0.22492262]), 'test_f1_macro': array([0.50938318, 0.52537279, 0.52832796, 0.53412986, 0.53577137]), 'test_f1_weighted': array([0.63303037, 0.6546687 , 0.65166775, 0.66217081, 0.63972638]), 'test_balanced_accuracy': array([0.51919935, 0.53233058, 0.53878713, 0.54141757, 0.56252737])}</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[0.74887706 0.42303254 0.87381347 ... 0.57360753 0.60529672 0.73882075]</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.635851915999134</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8038595381208479</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7052456286427977</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7513305736250739</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[[ 396  620]
+ [1062 2541]]</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2716049382716049, 'recall': 0.38976377952755903, 'f1-score': 0.32012934518997577, 'support': 1016.0}, '1': {'precision': 0.8038595381208479, 'recall': 0.7052456286427977, 'f1-score': 0.7513305736250739, 'support': 3603.0}, 'accuracy': 0.635851915999134, 'macro avg': {'precision': 0.5377322381962264, 'recall': 0.5475047040851784, 'f1-score': 0.5357299594075249, 'support': 4619.0}, 'weighted avg': {'precision': 0.6867842678357579, 'recall': 0.635851915999134, 'f1-score': 0.6564831070543747, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.78016028, ..., 0.92      , 0.95454545,
+       1.        ]), 'recalls': array([1.        , 0.99972245, 0.99972245, ..., 0.00638357, 0.00582848,
+       0.        ]), 'thresholds': array([0.0917136 , 0.10666667, 0.13423993, ..., 0.99230769, 0.99259259,
+       1.        ]), 'average_precision': 0.8209626002779904}</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 9.84251969e-04, 1.96850394e-03, ...,
+       9.97047244e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.        , 0.00582848, 0.00638357, ..., 0.99972245, 0.99972245,
+       1.        ]), 'thresholds': array([       inf, 1.        , 0.99259259, ..., 0.14291126, 0.10666667,
+       0.0917136 ]), 'roc_auc': 0.57316914928723}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 GradientBoostingClassifier(learning_rate=0.05, max_depth=5,
+                                            n_estimators=400, subsample=0.7))])</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_gb.pkl</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[0.60064935 0.64285714 0.63311688 0.62012987 0.61971831]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([3.16127396, 3.14523411, 3.15405941, 3.15622783, 3.13769674]), 'score_time': array([0.02400398, 0.02367067, 0.02399969, 0.02396059, 0.02431607]), 'test_accuracy': array([0.5995671 , 0.62121212, 0.62770563, 0.61796537, 0.62296858]), 'test_precision': array([0.7897351 , 0.79120879, 0.79591837, 0.79773463, 0.81740614]), 'test_recall': array([0.6625    , 0.69902913, 0.70319001, 0.68377254, 0.66527778]), 'test_f1': array([0.72054381, 0.74226804, 0.7466863 , 0.73637043, 0.73353752]), 'test_roc_auc': array([0.55824483, 0.56780061, 0.56143288, 0.56891427, 0.5841954 ]), 'test_average_precision': array([0.81576076, 0.82665092, 0.81200079, 0.82844452, 0.82638638]), 'test_neg_log_loss': array([-0.6618518 , -0.64210528, -0.65736174, -0.64830738, -0.65992384]), 'test_neg_brier_score': array([-0.23269316, -0.22537603, -0.2293953 , -0.22828115, -0.23256073]), 'test_f1_macro': array([0.50721847, 0.51399116, 0.52232274, 0.52142686, 0.54454654]), 'test_f1_weighted': array([0.6263482 , 0.64196456, 0.64810231, 0.64192553, 0.65040606]), 'test_balanced_accuracy': array([0.51997549, 0.52192836, 0.53139796, 0.5340045 , 0.56909209])}</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[0.74489877 0.47038087 0.84457292 ... 0.59836738 0.48438562 0.81075981]</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6180991556613986</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8043694141012909</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.6744379683597003</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.7336956521739131</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[[ 425  591]
+ [1173 2430]]</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.26595744680851063, 'recall': 0.4183070866141732, 'f1-score': 0.32517214996174443, 'support': 1016.0}, '1': {'precision': 0.8043694141012909, 'recall': 0.6744379683597003, 'f1-score': 0.7336956521739131, 'support': 3603.0}, 'accuracy': 0.6180991556613986, 'macro avg': {'precision': 0.5351634304549008, 'recall': 0.5463725274869368, 'f1-score': 0.5294339010678287, 'support': 4619.0}, 'weighted avg': {'precision': 0.6859397629279926, 'recall': 0.6180991556613986, 'f1-score': 0.643836401633198, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.78020788, 0.78016028, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 1.00000000e+00, 9.99722454e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.03736527, 0.04242065, 0.04343654, ..., 0.99496849, 0.99645639,
+       0.99741867]), 'average_precision': 0.8197411522786455}</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99901575, 0.99901575,
+       1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 1.66527893e-03, ...,
+       9.98612268e-01, 1.00000000e+00, 1.00000000e+00]), 'thresholds': array([       inf, 0.99741867, 0.99204598, ..., 0.08388173, 0.04242065,
+       0.03736527]), 'roc_auc': 0.5679273177863592}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=AdaBoostClassifier(algorithm='SAMME',
+                                                                     estimator=DecisionTreeClassifier(criterion='log_loss',
+                                                                                                      max_depth=5,
+                                                                                                      max_features='log2',
+                                                                                                      min_samples_leaf=2,
+                                                                                                      min_samples_split=5),
+                                                                     learning_rate=0.5,
+                                                                     n_estimators=1000,
+                                                                     random_state=42)))])</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_ada_samme_calibrated_sigmoid.pkl</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[0.56709957 0.63095238 0.5952381  0.60930736 0.61755146]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([31.23532867, 31.07733393, 31.12052751, 31.08306479, 31.17445087]), 'score_time': array([0.62467933, 0.6351521 , 0.62542725, 0.63313031, 0.6358881 ]), 'test_accuracy': array([0.56709957, 0.63095238, 0.5952381 , 0.60930736, 0.61755146]), 'test_precision': array([0.8125    , 0.81561462, 0.82429907, 0.81034483, 0.82136602]), 'test_recall': array([0.57777778, 0.68099861, 0.61165049, 0.6518724 , 0.65138889]), 'test_f1': array([0.67532468, 0.74225246, 0.7022293 , 0.72252114, 0.72656855]), 'test_roc_auc': array([0.58417075, 0.59057959, 0.60369766, 0.58298545, 0.61003695]), 'test_average_precision': array([0.83204222, 0.83058572, 0.83810775, 0.83654076, 0.8395016 ]), 'test_neg_log_loss': array([-0.65357053, -0.64114365, -0.64608138, -0.64355327, -0.64557086]), 'test_neg_brier_score': array([-0.23171348, -0.22524457, -0.22875147, -0.22760132, -0.22799745]), 'test_f1_macro': array([0.51298701, 0.54636432, 0.53523627, 0.53127885, 0.54526626]), 'test_f1_weighted': array([0.60364311, 0.6561804 , 0.62885357, 0.63849044, 0.64681911]), 'test_balanced_accuracy': array([0.55359477, 0.56710029, 0.57429815, 0.55500024, 0.57446292])}</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[0.64404664 0.46852362 0.73798851 ... 0.49461908 0.51310943 0.59452395]</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6040268456375839</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8167857142857143</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.6347488204274216</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7143526471966266</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[[ 503  513]
+ [1316 2287]]</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2765255634964266, 'recall': 0.4950787401574803, 'f1-score': 0.3548500881834215, 'support': 1016.0}, '1': {'precision': 0.8167857142857143, 'recall': 0.6347488204274216, 'f1-score': 0.7143526471966266, 'support': 3603.0}, 'accuracy': 0.6040268456375839, 'macro avg': {'precision': 0.5466556388910705, 'recall': 0.564913780292451, 'f1-score': 0.5346013676900241, 'support': 4619.0}, 'weighted avg': {'precision': 0.6979495347659229, 'recall': 0.6040268456375839, 'f1-score': 0.6352760938393163, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.78020788, 0.78016028, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 1.00000000e+00, 9.99722454e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.13930343, 0.18702245, 0.18771095, ..., 0.99147141, 0.99458431,
+       0.99639962]), 'average_precision': 0.8344284556250349}</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99901575, 0.99901575,
+       1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 8.04884818e-03, ...,
+       9.99444907e-01, 1.00000000e+00, 1.00000000e+00]), 'thresholds': array([       inf, 0.99639962, 0.97759357, ..., 0.18867609, 0.18702245,
+       0.13930343]), 'roc_auc': 0.5941255482635861}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=AdaBoostClassifier(algorithm='SAMME',
+                                                                     estimator=DecisionTreeClassifier(criterion='log_loss',
+                                                                                                      max_depth=5,
+                                                                                                      max_features='log2',
+                                                                                                      min_samples_leaf=2,
+                                                                                                      min_samples_split=5),
+                                                                     learning_rate=0.5,
+                                                                     n_estimators=1000,
+                                                                     random_state=42),
+                                        method='isotonic'))])</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_ada_samme_calibrated_isotonic.pkl</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[0.51948052 0.6017316  0.54329004 0.58549784 0.58938245]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([31.38443828, 31.40927386, 31.46735954, 31.72430229, 31.30988693]), 'score_time': array([0.62381434, 0.62193918, 0.63545942, 0.63970518, 0.6417141 ]), 'test_accuracy': array([0.51948052, 0.6017316 , 0.54329004, 0.58549784, 0.58938245]), 'test_precision': array([0.82701422, 0.81349911, 0.82012848, 0.82751938, 0.83497053]), 'test_recall': array([0.48472222, 0.63522885, 0.53120666, 0.59223301, 0.59027778]), 'test_f1': array([0.61120841, 0.71339564, 0.64478114, 0.69037995, 0.6916192 ]), 'test_roc_auc': array([0.57883306, 0.58687646, 0.60435014, 0.58648361, 0.611354  ]), 'test_average_precision': array([0.82956636, 0.83002248, 0.83728405, 0.83756212, 0.84085476]), 'test_neg_log_loss': array([-0.69524516, -0.64035528, -0.65316728, -0.64304911, -0.64545168]), 'test_neg_brier_score': array([-0.23443775, -0.22580591, -0.23230792, -0.22832713, -0.22847426]), 'test_f1_macro': array([0.49115661, 0.53045668, 0.5026936 , 0.53176935, 0.53867832]), 'test_f1_weighted': array([0.55819852, 0.63301337, 0.58234874, 0.62068742, 0.6243451 ]), 'test_balanced_accuracy': array([0.56343954, 0.55899373, 0.55870678, 0.57690468, 0.58824234])}</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[0.68460971 0.43892605 0.83504149 ... 0.47794331 0.49408308 0.56945842]</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5678718337302446</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8243843358901898</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5667499306133778</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6717105263157894</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[[ 581  435]
+ [1561 2042]]</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.27124183006535946, 'recall': 0.5718503937007874, 'f1-score': 0.36795440151994935, 'support': 1016.0}, '1': {'precision': 0.8243843358901898, 'recall': 0.5667499306133778, 'f1-score': 0.6717105263157894, 'support': 3603.0}, 'accuracy': 0.5678718337302446, 'macro avg': {'precision': 0.5478130829777746, 'recall': 0.5693001621570826, 'f1-score': 0.5198324639178694, 'support': 4619.0}, 'weighted avg': {'precision': 0.7027145402811776, 'recall': 0.5678718337302446, 'f1-score': 0.6048960160770854, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.78020788, 0.78016028, ..., 0.97297297, 0.97222222,
+       1.        ]), 'recalls': array([1.        , 1.        , 0.99972245, ..., 0.00999167, 0.00971413,
+       0.        ]), 'thresholds': array([0.11462451, 0.183527  , 0.18979812, ..., 0.992     , 0.99996235,
+       1.        ]), 'average_precision': 0.834491936188817}</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 9.84251969e-04, 9.84251969e-04, ...,
+       9.99015748e-01, 9.99015748e-01, 1.00000000e+00]), 'tpr': array([0.        , 0.00971413, 0.01026922, ..., 0.99972245, 1.        ,
+       1.        ]), 'thresholds': array([       inf, 1.        , 0.992     , ..., 0.18979812, 0.183527  ,
+       0.11462451]), 'roc_auc': 0.5940349905262674}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 AdaBoostClassifier(algorithm='SAMME',
+                                    estimator=DecisionTreeClassifier(criterion='log_loss',
+                                                                     max_depth=5,
+                                                                     max_features='log2',
+                                                                     min_samples_leaf=2,
+                                                                     min_samples_split=5),
+                                    learning_rate=0.5, n_estimators=1000,
+                                    random_state=42))])</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_ada_samme.pkl</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[0.55844156 0.61147186 0.57034632 0.57792208 0.61538462]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([7.52215981, 7.56435442, 7.54749584, 7.58003402, 7.55740166]), 'score_time': array([0.1933198 , 0.19718766, 0.19102407, 0.19785023, 0.19618464]), 'test_accuracy': array([0.55844156, 0.61147186, 0.57034632, 0.57792208, 0.61538462]), 'test_precision': array([0.812     , 0.81643357, 0.82142857, 0.81167608, 0.83363803]), 'test_recall': array([0.56388889, 0.64771151, 0.5742025 , 0.59778086, 0.63333333]), 'test_f1': array([0.66557377, 0.72235112, 0.67591837, 0.6884984 , 0.71981058]), 'test_roc_auc': array([0.58127723, 0.57617704, 0.6094983 , 0.59651346, 0.6130234 ]), 'test_average_precision': array([0.82526365, 0.82814656, 0.8389919 , 0.843835  , 0.84040883]), 'test_neg_log_loss': array([-0.67238403, -0.6682645 , -0.67175669, -0.66890537, -0.67122073]), 'test_neg_brier_score': array([-0.23993291, -0.23799132, -0.2396065 , -0.23824951, -0.23935986]), 'test_f1_macro': array([0.50794612, 0.53775214, 0.5193396 , 0.51706799, 0.55334225]), 'test_f1_weighted': array([0.59597195, 0.64123945, 0.60711861, 0.61317292, 0.64658615]), 'test_balanced_accuracy': array([0.55155229, 0.56523507, 0.56542637, 0.55258501, 0.59252874])}</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[0.52456404 0.48695815 0.55607384 ... 0.49045441 0.51448933 0.53593825]</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5867070794544273</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8191409193669932</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.6033860671662503</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6949017100847051</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[[ 536  480]
+ [1429 2174]]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2727735368956743, 'recall': 0.5275590551181102, 'f1-score': 0.3596108688359611, 'support': 1016.0}, '1': {'precision': 0.8191409193669932, 'recall': 0.6033860671662503, 'f1-score': 0.6949017100847051, 'support': 3603.0}, 'accuracy': 0.5867070794544273, 'macro avg': {'precision': 0.5459572281313337, 'recall': 0.5654725611421803, 'f1-score': 0.5272562894603331, 'support': 4619.0}, 'weighted avg': {'precision': 0.6989613868727607, 'recall': 0.5867070794544273, 'f1-score': 0.6211507911176725, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.78016028, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99722454e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.37078676, 0.38806971, 0.39445252, ..., 0.82401302, 0.83362932,
+       0.83880245]), 'average_precision': 0.8334534325689961}</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99901575, 1.        ,
+       1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 5.55092978e-04, ...,
+       9.99722454e-01, 9.99722454e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.83880245, 0.83362932, ..., 0.39445252, 0.38806971,
+       0.37078676]), 'roc_auc': 0.5933594270741137}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=BaggingClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                                                                     max_depth=5,
+                                                                                                     max_features='sqrt',
+                                                                                                     min_samples_split=5),
+                                                                    max_samples=100,
+                                                                    n_estimators=500,
+                                                                    n_jobs=-1,
+                                                                    random_state=42,
+                                                                    verbose=1)))])</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_bagging_bagpast_calibrated_sigmoid.pkl</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']/bagging=True</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[0.57142857 0.60606061 0.55735931 0.59415584 0.5915493 ]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.76255322, 0.73455405, 0.72561669, 0.75830698, 0.72025633]), 'score_time': array([0.62166023, 0.63470578, 0.64213181, 0.69689131, 0.62245083]), 'test_accuracy': array([0.57142857, 0.60606061, 0.55735931, 0.59415584, 0.5915493 ]), 'test_precision': array([0.8253012 , 0.82752294, 0.83913043, 0.85162602, 0.82542694]), 'test_recall': array([0.57083333, 0.62552011, 0.53536755, 0.58113731, 0.60416667]), 'test_f1': array([0.67487685, 0.71248025, 0.65368332, 0.69084913, 0.69767442]), 'test_roc_auc': array([0.59349129, 0.62087413, 0.61421261, 0.64379659, 0.62750411]), 'test_average_precision': array([0.83009236, 0.83984001, 0.83587383, 0.85619329, 0.84980092]), 'test_neg_log_loss': array([-0.67086739, -0.65052956, -0.6655961 , -0.65698265, -0.65969636]), 'test_neg_brier_score': array([-0.23913364, -0.22930969, -0.23664931, -0.23231761, -0.23372071]), 'test_f1_macro': array([0.52315271, 0.54352535, 0.52024496, 0.55014898, 0.53414606]), 'test_f1_weighted': array([0.60788177, 0.63824249, 0.59505131, 0.62902634, 0.6257432 ]), 'test_balanced_accuracy': array([0.57218137, 0.58123296, 0.58541776, 0.6107657 , 0.57548235])}</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[0.6347032  0.49614436 0.68792973 ... 0.45711385 0.48720355 0.50193887]</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.5841091145269539</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8334655035685964</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5834027199555926</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6863673469387755</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[[ 596  420]
+ [1501 2102]]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2842155460181211, 'recall': 0.5866141732283464, 'f1-score': 0.38291037584323806, 'support': 1016.0}, '1': {'precision': 0.8334655035685964, 'recall': 0.5834027199555926, 'f1-score': 0.6863673469387755, 'support': 3603.0}, 'accuracy': 0.5841091145269539, 'macro avg': {'precision': 0.5588405247933588, 'recall': 0.5850084465919695, 'f1-score': 0.5346388613910068, 'support': 4619.0}, 'weighted avg': {'precision': 0.7126519168893838, 'recall': 0.5841091145269539, 'f1-score': 0.6196186388562759, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.77994369, ..., 0.5       , 0.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99444907e-01, ...,
+       2.77546489e-04, 0.00000000e+00, 0.00000000e+00]), 'thresholds': array([0.25529018, 0.25554557, 0.25686089, ..., 0.74101031, 0.74458438,
+       0.75147232]), 'average_precision': 0.8404583947231186}</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 9.84251969e-04, 9.84251969e-04, ...,
+       9.95078740e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.        , 0.        , 0.00388565, ..., 0.99916736, 0.99916736,
+       1.        ]), 'thresholds': array([       inf, 0.75147232, 0.72306253, ..., 0.27165713, 0.25979595,
+       0.25529018]), 'roc_auc': 0.6200678131303529}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=BaggingClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                                                                     max_depth=5,
+                                                                                                     max_features='sqrt',
+                                                                                                     min_samples_split=5),
+                                                                    max_samples=100,
+                                                                    n_estimators=500,
+                                                                    n_jobs=-1,
+                                                                    random_state=42,
+                                                                    verbose=1),
+                                        method='isotonic'))])</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_bagging_bagpast_calibrated_isotonic.pkl</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']/bagging=True</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[0.59307359 0.6038961  0.52164502 0.58441558 0.58504875]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.77041411, 0.78308725, 0.77173543, 0.81600499, 0.77732587]), 'score_time': array([0.65944314, 0.63643003, 0.63308907, 0.64229274, 0.63362169]), 'test_accuracy': array([0.59307359, 0.6038961 , 0.52164502, 0.58441558, 0.58504875]), 'test_precision': array([0.81734317, 0.84332689, 0.84275184, 0.85031185, 0.82341651]), 'test_recall': array([0.61527778, 0.60471567, 0.47572816, 0.56726768, 0.59583333]), 'test_f1': array([0.70206022, 0.70436187, 0.60815603, 0.68053245, 0.69137792]), 'test_roc_auc': array([0.58776212, 0.62269494, 0.61037626, 0.63864843, 0.62605022]), 'test_average_precision': array([0.82687976, 0.83814565, 0.83456203, 0.85633749, 0.84786803]), 'test_neg_log_loss': array([-0.7087852 , -0.6476439 , -0.66642838, -0.65637497, -0.65572181]), 'test_neg_brier_score': array([-0.23971985, -0.22792227, -0.23712311, -0.23216857, -0.23205647]), 'test_f1_macro': array([0.530211  , 0.55218094, 0.49713357, 0.5430526 , 0.52916003]), 'test_f1_weighted': array([0.62617875, 0.63749449, 0.55937343, 0.62012464, 0.62002314]), 'test_balanced_accuracy': array([0.56499183, 0.60285045, 0.58022861, 0.60629394, 0.57131568])}</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[0.62404384 0.4690743  0.76031349 ... 0.46678337 0.46824837 0.48405234]</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.5776142022082702</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8346839546191248</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5717457674160422</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.678636139021578</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>[[ 608  408]
+ [1543 2060]]</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2826592282659228, 'recall': 0.5984251968503937, 'f1-score': 0.38395958320176826, 'support': 1016.0}, '1': {'precision': 0.8346839546191248, 'recall': 0.5717457674160422, 'f1-score': 0.678636139021578, 'support': 3603.0}, 'accuracy': 0.5776142022082702, 'macro avg': {'precision': 0.5586715914425238, 'recall': 0.585085482133218, 'f1-score': 0.5312978611116732, 'support': 4619.0}, 'weighted avg': {'precision': 0.7132600269345928, 'recall': 0.5776142022082702, 'f1-score': 0.6138187801315744, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.77994369, ..., 0.66666667, 0.5       ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99444907e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.07009524, 0.09164116, 0.09379487, ..., 0.95897436, 0.95938864,
+       1.        ]), 'average_precision': 0.8401892703853703}</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 9.84251969e-04, 9.84251969e-04, ...,
+       9.99015748e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 2.22037191e-03, ...,
+       9.98612268e-01, 9.98612268e-01, 1.00000000e+00]), 'thresholds': array([       inf, 1.        , 0.91555556, ..., 0.13442491, 0.13102357,
+       0.07009524]), 'roc_auc': 0.6180999921325404}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 BaggingClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                                    max_depth=5,
+                                                                    max_features='sqrt',
+                                                                    min_samples_split=5),
+                                   max_samples=100, n_estimators=500, n_jobs=-1,
+                                   random_state=42, verbose=1))])</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_bagging_bagpast.pkl</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']/bagging=True</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[0.55519481 0.60064935 0.54437229 0.58333333 0.5915493 ]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.09320641, 0.09218717, 0.08752251, 0.09544969, 0.09295654]), 'score_time': array([0.14319086, 0.13288569, 0.13550377, 0.14296365, 0.13803411]), 'test_accuracy': array([0.55519481, 0.60064935, 0.54437229, 0.58333333, 0.5915493 ]), 'test_precision': array([0.82389937, 0.82835821, 0.83333333, 0.85294118, 0.83172147]), 'test_recall': array([0.54583333, 0.61581137, 0.52011096, 0.5631068 , 0.59722222]), 'test_f1': array([0.6566416 , 0.70644391, 0.64047822, 0.67836257, 0.6952304 ]), 'test_roc_auc': array([0.59345724, 0.61917288, 0.61440391, 0.64161024, 0.62693623]), 'test_average_precision': array([0.82906742, 0.8401612 , 0.83458429, 0.85738649, 0.84712477]), 'test_neg_log_loss': array([-0.67609203, -0.66046066, -0.67355513, -0.66270641, -0.66535646]), 'test_neg_brier_score': array([-0.24159833, -0.23398795, -0.24048009, -0.23514442, -0.23645462]), 'test_f1_macro': array([0.5126526 , 0.54103922, 0.50930854, 0.54348236, 0.53809139]), 'test_f1_weighted': array([0.59306204, 0.63376609, 0.58284306, 0.61909703, 0.62610966]), 'test_balanced_accuracy': array([0.56703431, 0.5813047 , 0.57532641, 0.6091396 , 0.5843254 ])}</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[0.63662142 0.51715287 0.67680727 ... 0.43995104 0.4781211  0.50686387]</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.5750162372807968</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8338762214983714</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5684152095475993</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6760191450734445</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[[ 608  408]
+ [1555 2048]]</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.2810910772075821, 'recall': 0.5984251968503937, 'f1-score': 0.3825102233406732, 'support': 1016.0}, '1': {'precision': 0.8338762214983714, 'recall': 0.5684152095475993, 'f1-score': 0.6760191450734445, 'support': 3603.0}, 'accuracy': 0.5750162372807968, 'macro avg': {'precision': 0.5574836493529767, 'recall': 0.5834202031989966, 'f1-score': 0.5292646842070589, 'support': 4619.0}, 'weighted avg': {'precision': 0.7122850315006573, 'recall': 0.5750162372807968, 'f1-score': 0.6114586201805032, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.77994369, ..., 0.5       , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99444907e-01, ...,
+       2.77546489e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.22632921, 0.2306831 , 0.23606046, ..., 0.77098579, 0.77504816,
+       0.77999034]), 'average_precision': 0.8401960058503061}</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 0.00000000e+00, 9.84251969e-04, ...,
+       9.99015748e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 2.77546489e-04, ...,
+       9.99444907e-01, 9.99444907e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.77999034, 0.77504816, ..., 0.23660045, 0.23606046,
+       0.22632921]), 'roc_auc': 0.6193179458937325}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=BaggingClassifier(bootstrap=False,
+                                                                    estimator=DecisionTreeClassifier(criterion='entropy',
+                                                                                                     max_depth=5,
+                                                                                                     max_features='sqrt',
+                                                                                                     min_samples_split=5),
+                                                                    max_samples=100,
+                                                                    n_estimators=500,
+                                                                    n_jobs=-1,
+                                                                    random_state=42,
+                                                                    verbose=1)))])</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_bagpast_calibrated_sigmoid.pkl</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']/bagging=False</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[0.57142857 0.6017316  0.55519481 0.59090909 0.58504875]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.796808  , 0.77581048, 0.79530525, 0.79131031, 0.79428887]), 'score_time': array([0.70951915, 0.63231134, 0.66770363, 0.65128589, 0.66196561]), 'test_accuracy': array([0.57142857, 0.6017316 , 0.55519481, 0.59090909, 0.58504875]), 'test_precision': array([0.82270916, 0.82745826, 0.83549784, 0.84787018, 0.83104126]), 'test_recall': array([0.57361111, 0.6185853 , 0.53536755, 0.57975035, 0.5875    ]), 'test_f1': array([0.67594108, 0.70793651, 0.65257819, 0.68863262, 0.68836452]), 'test_roc_auc': array([0.59279684, 0.62049152, 0.61363869, 0.64292888, 0.63055556]), 'test_average_precision': array([0.8298395 , 0.84050845, 0.83468325, 0.85748366, 0.85091803]), 'test_neg_log_loss': array([-0.67005472, -0.65006314, -0.6668741 , -0.65789935, -0.65961019]), 'test_neg_brier_score': array([-0.23873469, -0.22905993, -0.23727242, -0.23280858, -0.23374839]), 'test_f1_macro': array([0.52167661, 0.54104308, 0.51726654, 0.54620905, 0.53380949]), 'test_f1_weighted': array([0.6078243 , 0.63460455, 0.59312307, 0.62605257, 0.6203804 ]), 'test_balanced_accuracy': array([0.5686683 , 0.58022861, 0.58049165, 0.60514611, 0.58192734])}</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[0.62861072 0.51642778 0.68790717 ... 0.45882259 0.47185951 0.51039486]</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5808616583676121</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8327345309381238</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.578961976131002</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.6830386378519974</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>[[ 597  419]
+ [1517 2086]]</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.28240302743614004, 'recall': 0.5875984251968503, 'f1-score': 0.3814696485623003, 'support': 1016.0}, '1': {'precision': 0.8327345309381238, 'recall': 0.578961976131002, 'f1-score': 0.6830386378519974, 'support': 3603.0}, 'accuracy': 0.580861658367612, 'macro avg': {'precision': 0.5575687791871319, 'recall': 0.5832802006639262, 'f1-score': 0.5322541432071488, 'support': 4619.0}, 'weighted avg': {'precision': 0.7116830462968561, 'recall': 0.580861658367612, 'f1-score': 0.6167052121931248, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.78016028, ..., 0.5       , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99722454e-01, ...,
+       2.77546489e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.25743633, 0.26230404, 0.26251023, ..., 0.73346003, 0.73703612,
+       0.74133053]), 'average_precision': 0.8416658280327214}</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 0.00000000e+00, 9.84251969e-04, ...,
+       9.99015748e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 2.77546489e-04, ...,
+       9.99722454e-01, 9.99722454e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.74133053, 0.73703612, ..., 0.26251023, 0.26230404,
+       0.25743633]), 'roc_auc': 0.6200740961709511}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 CalibratedClassifierCV(estimator=BaggingClassifier(bootstrap=False,
+                                                                    estimator=DecisionTreeClassifier(criterion='entropy',
+                                                                                                     max_depth=5,
+                                                                                                     max_features='sqrt',
+                                                                                                     min_samples_split=5),
+                                                                    max_samples=100,
+                                                                    n_estimators=500,
+                                                                    n_jobs=-1,
+                                                                    random_state=42,
+                                                                    verbose=1),
+                                        method='isotonic'))])</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_bagpast_calibrated_isotonic.pkl</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']/bagging=False</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[0.57034632 0.5974026  0.51623377 0.59090909 0.57096425]</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.78193259, 0.83208227, 0.76120996, 0.78998637, 0.7641263 ]), 'score_time': array([0.64577055, 0.62321353, 0.64498901, 0.64591479, 0.6350925 ]), 'test_accuracy': array([0.57034632, 0.5974026 , 0.51623377, 0.59090909, 0.57096425]), 'test_precision': array([0.82892057, 0.84015595, 0.83910891, 0.84507042, 0.83471074]), 'test_recall': array([0.56527778, 0.59778086, 0.47018031, 0.58252427, 0.56111111]), 'test_f1': array([0.67217176, 0.69854133, 0.60266667, 0.68965517, 0.67109635]), 'test_roc_auc': array([0.59521718, 0.61998251, 0.6141272 , 0.63953322, 0.6284517 ]), 'test_average_precision': array([0.83123191, 0.83697047, 0.83560969, 0.85755345, 0.84561738]), 'test_neg_log_loss': array([-0.70756874, -0.64681825, -0.70479725, -0.65784168, -0.65838121]), 'test_neg_brier_score': array([-0.2387863 , -0.22796518, -0.23799905, -0.23303439, -0.23309444]), 'test_f1_macro': array([0.52446892, 0.54633907, 0.4922047 , 0.54482759, 0.52713696]), 'test_f1_weighted': array([0.60695233, 0.63166458, 0.55413035, 0.62601881, 0.60777293]), 'test_balanced_accuracy': array([0.57675654, 0.59691999, 0.57499163, 0.60160696, 0.58351122])}</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[0.62275322 0.50196377 0.79508081 ... 0.46919419 0.48094054 0.50367133]</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5691708161939814</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.837588949351193</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5553705245628643</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.667890520694259</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[[ 628  388]
+ [1602 2001]]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.28161434977578476, 'recall': 0.6181102362204725, 'f1-score': 0.3869377695625385, 'support': 1016.0}, '1': {'precision': 0.837588949351193, 'recall': 0.5553705245628643, 'f1-score': 0.667890520694259, 'support': 3603.0}, 'accuracy': 0.5691708161939814, 'macro avg': {'precision': 0.5596016495634889, 'recall': 0.5867403803916684, 'f1-score': 0.5274141451283988, 'support': 4619.0}, 'weighted avg': {'precision': 0.7152962034822571, 'recall': 0.5691708161939814, 'f1-score': 0.6060918640261863, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.77994369, ..., 0.5       , 0.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99444907e-01, ...,
+       2.77546489e-04, 0.00000000e+00, 0.00000000e+00]), 'thresholds': array([0.        , 0.07026194, 0.09172779, ..., 0.95      , 0.98181818,
+       1.        ]), 'average_precision': 0.8404871805776728}</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 9.84251969e-04, 9.84251969e-04, ...,
+       9.97047244e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.00000000e+00, 0.00000000e+00, 5.55092978e-04, ...,
+       9.98889814e-01, 9.98889814e-01, 1.00000000e+00]), 'thresholds': array([       inf, 1.        , 0.95      , ..., 0.13882968, 0.11882607,
+       0.        ]), 'roc_auc': 0.6190207307558662}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 BaggingClassifier(bootstrap=False,
+                                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                                    max_depth=5,
+                                                                    max_features='sqrt',
+                                                                    min_samples_split=5),
+                                   max_samples=100, n_estimators=500, n_jobs=-1,
+                                   random_state=42, verbose=1))])</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_bagpast.pkl</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']/bagging=False</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[0.56168831 0.60497835 0.53679654 0.59199134 0.57963164]</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.09978604, 0.09858155, 0.09927201, 0.10122514, 0.10166049]), 'score_time': array([0.12562156, 0.12071896, 0.12620926, 0.12769628, 0.12414217]), 'test_accuracy': array([0.56168831, 0.60497835, 0.53679654, 0.59199134, 0.57963164]), 'test_precision': array([0.8343949 , 0.83584906, 0.83990719, 0.86595745, 0.82677165]), 'test_recall': array([0.54583333, 0.61442441, 0.50208044, 0.56449376, 0.58333333]), 'test_f1': array([0.65994962, 0.70823341, 0.62847222, 0.68345928, 0.68403909]), 'test_roc_auc': array([0.59277642, 0.61892691, 0.61805238, 0.64549784, 0.62688834]), 'test_average_precision': array([0.82635604, 0.84036661, 0.83423748, 0.86095952, 0.84770742]), 'test_neg_log_loss': array([-0.67934046, -0.65661071, -0.67757165, -0.66638581, -0.6705274 ]), 'test_neg_brier_score': array([-0.24307675, -0.2322554 , -0.24236292, -0.2367792 , -0.23881455]), 'test_f1_macro': array([0.52175563, 0.54842156, 0.50676485, 0.55481944, 0.52810369]), 'test_f1_weighted': array([0.5989289 , 0.63801306, 0.57499474, 0.62693571, 0.61544778]), 'test_balanced_accuracy': array([0.5817402 , 0.59292649, 0.58108948, 0.62707447, 0.5749179 ])}</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[0.61851151 0.4843164  0.68360704 ... 0.44701505 0.47928392 0.50117782]</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.5750162372807968</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.8402489626556017</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5620316402997502</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.6735406618992184</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[[ 631  385]
+ [1578 2025]]</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.28564961521050247, 'recall': 0.6210629921259843, 'f1-score': 0.3913178294573643, 'support': 1016.0}, '1': {'precision': 0.8402489626556017, 'recall': 0.5620316402997502, 'f1-score': 0.6735406618992184, 'support': 3603.0}, 'accuracy': 0.5750162372807968, 'macro avg': {'precision': 0.5629492889330521, 'recall': 0.5915473162128673, 'f1-score': 0.5324292456782913, 'support': 4619.0}, 'weighted avg': {'precision': 0.7182587186624818, 'recall': 0.5750162372807968, 'f1-score': 0.6114626368373167, 'support': 4619.0}}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78003897, 0.77999134, 0.77994369, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99444907e-01, ...,
+       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.20139228, 0.21173839, 0.21645226, ..., 0.74563369, 0.74795003,
+       0.74856036]), 'average_precision': 0.8411586796077131}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99704724, 1.        ,
+       1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 1.94282542e-03, ...,
+       9.99444907e-01, 9.99444907e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.74856036, 0.739182  , ..., 0.23113555, 0.21645226,
+       0.20139228]), 'roc_auc': 0.6200593446843292}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('scaler', StandardScaler()), ('smote', SMOTE(random_state=42)),
+                ('model',
+                 VotingClassifier(estimators=[('rf',
+                                               CalibratedClassifierCV(estimator=RandomForestClassifier(bootstrap=False,
+                                                                                                       max_features='log2',
+                                                                                                       min_samples_split=5),
+                                                                      method='isotonic')),
+                                              ('lg',
+                                               CalibratedClassifierCV(estimator=LogisticRegression(C=0.75,
+                                                                                                   class_weight='balanced',
+                                                                                                   max_iter=500),
+                                                                      method='isotonic')),
+                                              ('svc',
+                                               CalibratedClassifierCV(estimator=SVC(C=0.01,
+                                                                                    gamma=1.0,
+                                                                                    probability=True,
+                                                                                    random_state=42),
+                                                                      method='isotonic'))],
+                                  n_jobs=-1, verbose=2, voting='soft'))])</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\under_over\inconsistent\fit\best_models\mean_under_over_1_5_soft_voting_calibrated_isotonic.pkl</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>predict_proba</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[0.67243243 0.68756757 0.68073593 0.66883117 0.6969697 ]</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([10.58399129, 10.58345318, 10.45932269, 10.40702605, 10.37104344]), 'score_time': array([1.69998002, 1.69809389, 1.69759154, 1.68250775, 1.70017624]), 'test_accuracy': array([0.66918919, 0.69081081, 0.67857143, 0.67099567, 0.69805195]), 'test_precision': array([0.80380673, 0.80277778, 0.80813953, 0.80797637, 0.81571429]), 'test_recall': array([0.76144244, 0.80055402, 0.77115118, 0.75866852, 0.79195562]), 'test_f1': array([0.78205128, 0.80166436, 0.78921221, 0.78254649, 0.80365939]), 'test_roc_auc': array([0.60531397, 0.6066175 , 0.60673463, 0.59831378, 0.61215608]), 'test_average_precision': array([0.84622425, 0.8512771 , 0.84315407, 0.83813633, 0.83355924]), 'test_neg_log_loss': array([-0.62228197, -0.60801971, -0.61373022, -0.62369117, -0.60863417]), 'test_neg_brier_score': array([-0.21588531, -0.20947852, -0.21212844, -0.21661026, -0.20939719]), 'test_f1_macro': array([0.54797631, 0.55034198, 0.55633731, 0.55349547, 0.57513181]), 'test_f1_weighted': array([0.67880524, 0.69135421, 0.68688839, 0.68190286, 0.70324576]), 'test_balanced_accuracy': array([0.55228985, 0.55052331, 0.56045244, 0.55913721, 0.57824382])}</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[0.64906238 0.62292436 0.55196627 ... 0.71559244 0.72733812 0.65548481]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.681306793595846</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.8069064748201439</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0.7775929007210205</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.7919785341053523</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[[ 345  671]
+ [ 802 2804]]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>{'0': {'precision': 0.3007846556233653, 'recall': 0.3395669291338583, 'f1-score': 0.31900138696255204, 'support': 1016.0}, '1': {'precision': 0.8069064748201439, 'recall': 0.7775929007210205, 'f1-score': 0.7919785341053523, 'support': 3606.0}, 'accuracy': 0.681306793595846, 'macro avg': {'precision': 0.5538455652217547, 'recall': 0.5585799149274394, 'f1-score': 0.5554899605339522, 'support': 4622.0}, 'weighted avg': {'precision': 0.6956516569266071, 'recall': 0.681306793595846, 'f1-score': 0.6880095203673416, 'support': 4622.0}}</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'precisions': array([0.78018174, 0.78013417, 0.78008658, ..., 0.        , 0.        ,
+       1.        ]), 'recalls': array([1.        , 0.99972268, 0.99944537, ..., 0.        , 0.        ,
+       0.        ]), 'thresholds': array([0.15150808, 0.20332998, 0.21535074, ..., 0.86164973, 0.8672749 ,
+       0.86907974]), 'average_precision': 0.840330395262948}</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>{'fpr': array([0.00000000e+00, 9.84251969e-04, 1.96850394e-03, ...,
+       9.99015748e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.        , 0.        , 0.        , ..., 0.99916805, 0.99916805,
+       1.        ]), 'thresholds': array([       inf, 0.86907974, 0.8672749 , ..., 0.21630504, 0.21589047,
+       0.15150808]), 'roc_auc': 0.6043487232565148}</t>
         </is>
       </c>
     </row>
